--- a/public/system/export/lab.xlsx
+++ b/public/system/export/lab.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>STT</t>
   </si>
@@ -113,7 +113,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -138,85 +138,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -228,23 +167,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -255,12 +182,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,191 +402,212 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E1008"/>
+  <dimension ref="A1:F1008"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="40.85546875" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="46.7109375" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:6" ht="15" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="16" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:6" ht="15" customHeight="1">
+      <c r="A2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="16" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
     </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1">
+    <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1">
+    <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1">
+    <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="17" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="13"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="15"/>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="7">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="6">
         <v>1</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
+      <c r="D10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="15"/>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A11" s="6">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A11" s="5">
         <v>2</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="13"/>
+      <c r="F11" s="15"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A12" s="6">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A12" s="5">
         <v>3</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="15"/>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A13" s="6">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A13" s="5">
         <v>4</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="15"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A14" s="6">
+    <row r="14" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A14" s="5">
         <v>5</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="11"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="13"/>
+      <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A15" s="6">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A15" s="5">
         <v>6</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A16" s="6">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A16" s="5">
         <v>7</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="11"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="6">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A17" s="5">
         <v>8</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="11"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A18" s="6">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A18" s="5">
         <v>9</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="15"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="6">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A19" s="5">
         <v>10</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="15"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1"/>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1634,24 +1586,24 @@
     <row r="1008" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/system/export/lab.xlsx
+++ b/public/system/export/lab.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>STT</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Tên Phòng Bộ Môn</t>
-  </si>
-  <si>
-    <t>Phòng thực hành</t>
   </si>
 </sst>
 </file>
@@ -173,6 +170,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -182,16 +189,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,26 +411,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="1"/>
@@ -442,13 +439,13 @@
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1">
       <c r="A5" s="1"/>
@@ -479,23 +476,17 @@
         <v>1</v>
       </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="15"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
       <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="15"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1">
       <c r="A11" s="5">
@@ -503,11 +494,9 @@
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="15"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
       <c r="A12" s="5">
@@ -515,11 +504,9 @@
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="15"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="10"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
       <c r="A13" s="5">
@@ -527,11 +514,9 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="15"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1">
       <c r="A14" s="5">
@@ -539,11 +524,9 @@
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="15"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="5">
@@ -551,9 +534,9 @@
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="15"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="10"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="5">
@@ -561,9 +544,9 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="15"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="10"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="5">
@@ -571,9 +554,9 @@
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="15"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="5">
@@ -581,9 +564,9 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="15"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
       <c r="A19" s="5">
@@ -591,9 +574,9 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="15"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="21" spans="1:6" ht="15.75" customHeight="1"/>
@@ -1586,22 +1569,22 @@
     <row r="1008" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
